--- a/DesignTable/Data/Table/Tables/SceneData.xlsx
+++ b/DesignTable/Data/Table/Tables/SceneData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698CC8B0-6524-47BF-A64B-7D2FB671F6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E11C0F0-AC9E-49D3-B109-906A81DB554E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4B5F7AFB-0092-4900-B3F4-0317E72BC1CA}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4B5F7AFB-0092-4900-B3F4-0317E72BC1CA}"/>
   </bookViews>
   <sheets>
     <sheet name="record" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>ColumnName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TableID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SceneName</t>
   </si>
   <si>
@@ -103,8 +99,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>FieldNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TableId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -161,7 +164,11 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -176,7 +183,7 @@
 
 <file path=xl/xmlMaps.xml><?xml version="1.0" encoding="utf-8"?>
 <MapInfo xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" SelectionNamespaces="">
-  <Schema ID="Schema1">
+  <Schema ID="Schema2">
     <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="">
       <xsd:element nillable="true" name="SceneData">
         <xsd:complexType>
@@ -191,6 +198,7 @@
                 <xsd:attribute name="EnumID" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="IDRule" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="StringHashIds" form="unqualified" type="xsd:string"/>
+                <xsd:attribute name="FieldNo" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="TableId" form="unqualified" type="xsd:string"/>
               </xsd:complexType>
             </xsd:element>
@@ -207,7 +215,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="1" Name="SceneData_맵" RootElement="SceneData" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="4" Name="SceneData_맵" RootElement="SceneData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -216,10 +224,10 @@
   <autoFilter ref="A1:B3" xr:uid="{A26CEE2A-890C-4B8D-BA15-C39169406FFC}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{1B80E520-F9B4-4CF0-8963-EDFDCE1A5557}" uniqueName="SceneName" name="SceneName">
-      <xmlColumnPr mapId="1" xpath="/SceneData/record/SceneName" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/SceneData/record/SceneName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{77D5F1D9-E8BE-48BC-8208-9E21CCAA55BC}" uniqueName="Path" name="Path">
-      <xmlColumnPr mapId="1" xpath="/SceneData/record/Path" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/SceneData/record/Path" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -227,35 +235,38 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76F54B0C-EC55-49F9-866C-FCCB2F8188B0}" name="표1" displayName="표1" ref="A1:I3" tableType="xml" totalsRowShown="0">
-  <autoFilter ref="A1:I3" xr:uid="{76F54B0C-EC55-49F9-866C-FCCB2F8188B0}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76F54B0C-EC55-49F9-866C-FCCB2F8188B0}" name="표1" displayName="표1" ref="A1:J3" tableType="xml" totalsRowShown="0">
+  <autoFilter ref="A1:J3" xr:uid="{76F54B0C-EC55-49F9-866C-FCCB2F8188B0}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{4711E2FC-E76F-461B-A2FA-7E2F13833BC8}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="1" xpath="/SceneData/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{C0012307-E22A-4099-9DD1-6208B10048E4}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="1" xpath="/SceneData/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{FCA2F235-7D04-43C2-8258-2996D5AD01AA}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="1" xpath="/SceneData/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{10D18428-9366-4C4E-BC6E-2FCDB97D7CF0}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="1" xpath="/SceneData/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{70267D30-4616-492C-8E2E-DE8C7CA7D9F8}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="1" xpath="/SceneData/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{59557864-90C6-44A5-8907-9A0A4B6DE7D4}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="1" xpath="/SceneData/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{64202E7C-6F7C-45BF-95EE-2F7A0B91F022}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="1" xpath="/SceneData/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{BDD3E26A-0802-437D-8462-84720283D73C}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="1" xpath="/SceneData/verify/@StringHashIds" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{5C1C9571-AC41-4E99-95EE-65FE595ED7EF}" uniqueName="TableId" name="TableID">
-      <xmlColumnPr mapId="1" xpath="/SceneData/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@StringHashIds" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{5C1C9571-AC41-4E99-95EE-65FE595ED7EF}" uniqueName="FieldNo" name="FieldNo">
+      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@FieldNo" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{7272092B-BBD9-436A-A6BF-BB9834C92DBF}" uniqueName="TableId" name="TableId" dataDxfId="0">
+      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -568,26 +579,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -601,10 +612,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8F6DB5-1F5D-4B04-9F8C-E83B46D69AC7}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -630,64 +641,73 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1024</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>1024</v>
       </c>
     </row>

--- a/DesignTable/Data/Table/Tables/SceneData.xlsx
+++ b/DesignTable/Data/Table/Tables/SceneData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E11C0F0-AC9E-49D3-B109-906A81DB554E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37B80AC2-9C1E-4792-AD2C-2405E7C42780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4B5F7AFB-0092-4900-B3F4-0317E72BC1CA}"/>
   </bookViews>
@@ -215,7 +215,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="4" Name="SceneData_맵" RootElement="SceneData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="6" Name="SceneData_맵" RootElement="SceneData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -224,10 +224,10 @@
   <autoFilter ref="A1:B3" xr:uid="{A26CEE2A-890C-4B8D-BA15-C39169406FFC}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{1B80E520-F9B4-4CF0-8963-EDFDCE1A5557}" uniqueName="SceneName" name="SceneName">
-      <xmlColumnPr mapId="4" xpath="/SceneData/record/SceneName" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/SceneData/record/SceneName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{77D5F1D9-E8BE-48BC-8208-9E21CCAA55BC}" uniqueName="Path" name="Path">
-      <xmlColumnPr mapId="4" xpath="/SceneData/record/Path" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/SceneData/record/Path" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -239,34 +239,34 @@
   <autoFilter ref="A1:J3" xr:uid="{76F54B0C-EC55-49F9-866C-FCCB2F8188B0}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{4711E2FC-E76F-461B-A2FA-7E2F13833BC8}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{C0012307-E22A-4099-9DD1-6208B10048E4}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{FCA2F235-7D04-43C2-8258-2996D5AD01AA}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{10D18428-9366-4C4E-BC6E-2FCDB97D7CF0}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{70267D30-4616-492C-8E2E-DE8C7CA7D9F8}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{59557864-90C6-44A5-8907-9A0A4B6DE7D4}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{64202E7C-6F7C-45BF-95EE-2F7A0B91F022}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{BDD3E26A-0802-437D-8462-84720283D73C}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{5C1C9571-AC41-4E99-95EE-65FE595ED7EF}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{7272092B-BBD9-436A-A6BF-BB9834C92DBF}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="4" xpath="/SceneData/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/SceneData.xlsx
+++ b/DesignTable/Data/Table/Tables/SceneData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37B80AC2-9C1E-4792-AD2C-2405E7C42780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49937877-B6DA-477F-BD64-D3085A90477B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4B5F7AFB-0092-4900-B3F4-0317E72BC1CA}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4B5F7AFB-0092-4900-B3F4-0317E72BC1CA}"/>
   </bookViews>
   <sheets>
     <sheet name="record" sheetId="2" r:id="rId1"/>

--- a/DesignTable/Data/Table/Tables/SceneData.xlsx
+++ b/DesignTable/Data/Table/Tables/SceneData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49937877-B6DA-477F-BD64-D3085A90477B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5099177C-1920-4991-9970-385AF3B8021F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4B5F7AFB-0092-4900-B3F4-0317E72BC1CA}"/>
   </bookViews>
@@ -215,7 +215,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="6" Name="SceneData_맵" RootElement="SceneData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="8" Name="SceneData_맵" RootElement="SceneData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -224,10 +224,10 @@
   <autoFilter ref="A1:B3" xr:uid="{A26CEE2A-890C-4B8D-BA15-C39169406FFC}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{1B80E520-F9B4-4CF0-8963-EDFDCE1A5557}" uniqueName="SceneName" name="SceneName">
-      <xmlColumnPr mapId="6" xpath="/SceneData/record/SceneName" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/SceneData/record/SceneName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{77D5F1D9-E8BE-48BC-8208-9E21CCAA55BC}" uniqueName="Path" name="Path">
-      <xmlColumnPr mapId="6" xpath="/SceneData/record/Path" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/SceneData/record/Path" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -239,34 +239,34 @@
   <autoFilter ref="A1:J3" xr:uid="{76F54B0C-EC55-49F9-866C-FCCB2F8188B0}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{4711E2FC-E76F-461B-A2FA-7E2F13833BC8}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{C0012307-E22A-4099-9DD1-6208B10048E4}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{FCA2F235-7D04-43C2-8258-2996D5AD01AA}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{10D18428-9366-4C4E-BC6E-2FCDB97D7CF0}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{70267D30-4616-492C-8E2E-DE8C7CA7D9F8}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{59557864-90C6-44A5-8907-9A0A4B6DE7D4}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{64202E7C-6F7C-45BF-95EE-2F7A0B91F022}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{BDD3E26A-0802-437D-8462-84720283D73C}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{5C1C9571-AC41-4E99-95EE-65FE595ED7EF}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{7272092B-BBD9-436A-A6BF-BB9834C92DBF}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="6" xpath="/SceneData/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/SceneData.xlsx
+++ b/DesignTable/Data/Table/Tables/SceneData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5099177C-1920-4991-9970-385AF3B8021F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F6A7814-E9CD-426D-B0FD-340C37EB22B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4B5F7AFB-0092-4900-B3F4-0317E72BC1CA}"/>
   </bookViews>
@@ -215,7 +215,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="8" Name="SceneData_맵" RootElement="SceneData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="9" Name="SceneData_맵" RootElement="SceneData" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -224,10 +224,10 @@
   <autoFilter ref="A1:B3" xr:uid="{A26CEE2A-890C-4B8D-BA15-C39169406FFC}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{1B80E520-F9B4-4CF0-8963-EDFDCE1A5557}" uniqueName="SceneName" name="SceneName">
-      <xmlColumnPr mapId="8" xpath="/SceneData/record/SceneName" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/SceneData/record/SceneName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{77D5F1D9-E8BE-48BC-8208-9E21CCAA55BC}" uniqueName="Path" name="Path">
-      <xmlColumnPr mapId="8" xpath="/SceneData/record/Path" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/SceneData/record/Path" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -239,34 +239,34 @@
   <autoFilter ref="A1:J3" xr:uid="{76F54B0C-EC55-49F9-866C-FCCB2F8188B0}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{4711E2FC-E76F-461B-A2FA-7E2F13833BC8}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/SceneData/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{C0012307-E22A-4099-9DD1-6208B10048E4}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/SceneData/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{FCA2F235-7D04-43C2-8258-2996D5AD01AA}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/SceneData/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{10D18428-9366-4C4E-BC6E-2FCDB97D7CF0}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/SceneData/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{70267D30-4616-492C-8E2E-DE8C7CA7D9F8}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/SceneData/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{59557864-90C6-44A5-8907-9A0A4B6DE7D4}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/SceneData/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{64202E7C-6F7C-45BF-95EE-2F7A0B91F022}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/SceneData/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{BDD3E26A-0802-437D-8462-84720283D73C}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/SceneData/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{5C1C9571-AC41-4E99-95EE-65FE595ED7EF}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/SceneData/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{7272092B-BBD9-436A-A6BF-BB9834C92DBF}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="8" xpath="/SceneData/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/SceneData/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/SceneData.xlsx
+++ b/DesignTable/Data/Table/Tables/SceneData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F6A7814-E9CD-426D-B0FD-340C37EB22B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB598FE2-B943-4680-BF5E-14E964F17358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4B5F7AFB-0092-4900-B3F4-0317E72BC1CA}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
   <si>
     <t>ColumnName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -108,6 +108,18 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>SampleSceneA</t>
+  </si>
+  <si>
+    <t>Assets/Scenes/Sample/SampleSceneA.unity</t>
+  </si>
+  <si>
+    <t>SampleSceneB</t>
+  </si>
+  <si>
+    <t>Assets/Scenes/Sample/SampleSceneB.unity</t>
   </si>
 </sst>
 </file>
@@ -220,8 +232,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A26CEE2A-890C-4B8D-BA15-C39169406FFC}" name="표2" displayName="표2" ref="A1:B3" tableType="xml" totalsRowShown="0">
-  <autoFilter ref="A1:B3" xr:uid="{A26CEE2A-890C-4B8D-BA15-C39169406FFC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A26CEE2A-890C-4B8D-BA15-C39169406FFC}" name="표2" displayName="표2" ref="A1:B5" tableType="xml" totalsRowShown="0">
+  <autoFilter ref="A1:B5" xr:uid="{A26CEE2A-890C-4B8D-BA15-C39169406FFC}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{1B80E520-F9B4-4CF0-8963-EDFDCE1A5557}" uniqueName="SceneName" name="SceneName">
       <xmlColumnPr mapId="9" xpath="/SceneData/record/SceneName" xmlDataType="string"/>
@@ -570,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A837AA-2A5E-410B-AAA7-25211C9FCF34}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.875" bestFit="1" customWidth="1"/>
@@ -601,6 +613,22 @@
         <v>17</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
